--- a/Clarifications/CAR_data_Activity_name_tagging_1Dec_for_final_ppt.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_1Dec_for_final_ppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F958D782-817C-4FC5-A7A5-BB7B7DD5990F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9470CA-A566-45B9-8680-28D1DB776253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="627" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -906,9 +906,6 @@
     <t>Negative / Neutral</t>
   </si>
   <si>
-    <t>If the caller has been to ['OtherLegalPersonalInjuryMenu','OtherLegalCriminalCaseMenu', or                                                       'OtherLegalOtherMenu','ClinicVoicemailTransfer' earlier, classify the calls as Neutral, type = "LAC does not serve". If the call has not been inside this menu, then Negative, and type = "Abandoned"</t>
-  </si>
-  <si>
     <t>Interpreter needed (FD, Legal menu)</t>
   </si>
   <si>
@@ -969,6 +966,9 @@
   <si>
     <t xml:space="preserve">Krish (1Dec): But the caller was not called back, leading to a failed callback, a negative outcome
 "Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
+  </si>
+  <si>
+    <t>If the caller has been to 'OtherLegalPersonalInjuryMenu','OtherLegalCriminalCaseMenu', or                                                       'OtherLegalOtherMenu' earlier, classify the calls as Neutral, type = "LAC does not serve". If the call has not been inside this menu, then Negative, and type = "Abandoned"</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1064,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1107,14 +1107,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4049,7 +4042,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -4062,7 +4055,7 @@
     <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="45">
+    <row r="1" spans="1:14" ht="45">
       <c r="A1" s="6" t="s">
         <v>196</v>
       </c>
@@ -4097,7 +4090,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="75">
+    <row r="2" spans="1:14" ht="75">
       <c r="A2" s="15" t="s">
         <v>37</v>
       </c>
@@ -4128,8 +4121,14 @@
       <c r="K2" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="30">
+      <c r="L2" t="str">
+        <f>_xlfn.CONCAT("last_act.loc[last_act['Activity Name'] == ","'",A2,"'", ", 'outcome'] = ","'",E2,"'",CHAR(10),"last_act.loc[last_act['Activity Name'] == ","'",A2,"'", ", 'outcome_type'] =","'", F2,"'",CHAR(10),"last_act.loc[last_act['Activity Name'] == ","'",A2,"'", ", 'outcome_source'] =","'", A2,"'")</f>
+        <v>last_act.loc[last_act['Activity Name'] == 'ClosedQueueMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'ClosedQueueMenu', 'outcome_type'] ='Closed queue'
+last_act.loc[last_act['Activity Name'] == 'ClosedQueueMenu', 'outcome_source'] ='ClosedQueueMenu'</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="30">
       <c r="A3" s="15" t="s">
         <v>40</v>
       </c>
@@ -4160,8 +4159,14 @@
       <c r="K3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="30">
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L66" si="1">_xlfn.CONCAT("last_act.loc[last_act['Activity Name'] == ","'",A3,"'", ", 'outcome'] = ","'",E3,"'",CHAR(10),"last_act.loc[last_act['Activity Name'] == ","'",A3,"'", ", 'outcome_type'] =","'", F3,"'",CHAR(10),"last_act.loc[last_act['Activity Name'] == ","'",A3,"'", ", 'outcome_source'] =","'", A3,"'")</f>
+        <v>last_act.loc[last_act['Activity Name'] == 'StaffDirectoryEnglishTransfer', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'StaffDirectoryEnglishTransfer', 'outcome_type'] ='Staff directory'
+last_act.loc[last_act['Activity Name'] == 'StaffDirectoryEnglishTransfer', 'outcome_source'] ='StaffDirectoryEnglishTransfer'</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="30">
       <c r="A4" s="15" t="s">
         <v>32</v>
       </c>
@@ -4192,8 +4197,14 @@
       <c r="K4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="105">
+      <c r="L4" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'LanguageSelectionMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'LanguageSelectionMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'LanguageSelectionMenu', 'outcome_source'] ='LanguageSelectionMenu'</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="105">
       <c r="A5" s="15" t="s">
         <v>41</v>
       </c>
@@ -4226,8 +4237,15 @@
       <c r="K5" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ClinicVoicemailTransfer', 'outcome'] = 'Positive / Negative / Neutral'
+last_act.loc[last_act['Activity Name'] == 'ClinicVoicemailTransfer', 'outcome_type'] ='multiple (check comment)'
+last_act.loc[last_act['Activity Name'] == 'ClinicVoicemailTransfer', 'outcome_source'] ='ClinicVoicemailTransfer'</v>
+      </c>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="15" t="s">
         <v>33</v>
       </c>
@@ -4258,8 +4276,14 @@
       <c r="K6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="165">
+      <c r="L6" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'MainMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'MainMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'MainMenu', 'outcome_source'] ='MainMenu'</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="165">
       <c r="A7" s="15" t="s">
         <v>44</v>
       </c>
@@ -4281,7 +4305,7 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>209</v>
@@ -4292,8 +4316,14 @@
       <c r="K7" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'DisconnectContact1', 'outcome'] = 'Neutral / Negative'
+last_act.loc[last_act['Activity Name'] == 'DisconnectContact1', 'outcome_type'] ='multiple (check comment)'
+last_act.loc[last_act['Activity Name'] == 'DisconnectContact1', 'outcome_source'] ='DisconnectContact1'</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="15" t="s">
         <v>36</v>
       </c>
@@ -4324,8 +4354,14 @@
       <c r="K8" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="105">
+      <c r="L8" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'LegalMenu2', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'LegalMenu2', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'LegalMenu2', 'outcome_source'] ='LegalMenu2'</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="105">
       <c r="A9" s="15" t="s">
         <v>55</v>
       </c>
@@ -4360,8 +4396,14 @@
       <c r="K9" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="62.25" customHeight="1">
+      <c r="L9" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'FarmworkerMainMenu', 'outcome'] = 'Negative '
+last_act.loc[last_act['Activity Name'] == 'FarmworkerMainMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'FarmworkerMainMenu', 'outcome_source'] ='FarmworkerMainMenu'</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="62.25" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
@@ -4394,8 +4436,14 @@
       <c r="K10" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="210">
+      <c r="L10" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SetCallerID', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'SetCallerID', 'outcome_type'] ='Connected to agent'
+last_act.loc[last_act['Activity Name'] == 'SetCallerID', 'outcome_source'] ='SetCallerID'</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="210">
       <c r="A11" s="15" t="s">
         <v>56</v>
       </c>
@@ -4428,12 +4476,18 @@
       <c r="K11" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" s="19" customFormat="1" ht="50.25" customHeight="1">
+      <c r="L11" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'LegalServerScreenPop', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'LegalServerScreenPop', 'outcome_type'] ='Connected to agent'
+last_act.loc[last_act['Activity Name'] == 'LegalServerScreenPop', 'outcome_source'] ='LegalServerScreenPop'</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="50.25" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="5" t="s">
         <v>213</v>
       </c>
       <c r="C12" s="10">
@@ -4443,27 +4497,33 @@
         <f t="shared" si="0"/>
         <v>3.1757915328326128E-2</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18" t="s">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="I12" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="K12" s="18">
+      <c r="I12" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K12" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer1', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer1', 'outcome_type'] ='No language selected (FD1)'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer1', 'outcome_source'] ='FrontDeskTransfer1'</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="15" t="s">
         <v>43</v>
       </c>
@@ -4481,7 +4541,7 @@
         <v>230</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -4494,8 +4554,14 @@
       <c r="K13" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ClosedMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'ClosedMenu', 'outcome_type'] ='Closed hours'
+last_act.loc[last_act['Activity Name'] == 'ClosedMenu', 'outcome_source'] ='ClosedMenu'</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="15" t="s">
         <v>68</v>
       </c>
@@ -4528,8 +4594,14 @@
       <c r="K14" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="120">
+      <c r="L14" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer2', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer2', 'outcome_type'] ='Appt / feedback'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer2', 'outcome_source'] ='FrontDeskTransfer2'</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="105">
       <c r="A15" s="15" t="s">
         <v>48</v>
       </c>
@@ -4551,7 +4623,7 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>212</v>
@@ -4562,8 +4634,14 @@
       <c r="K15" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="30">
+      <c r="L15" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'OtherLegalMenu', 'outcome'] = 'Negative / Neutral'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalMenu', 'outcome_type'] ='multiple (check comment)'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalMenu', 'outcome_source'] ='OtherLegalMenu'</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="30">
       <c r="A16" s="15" t="s">
         <v>72</v>
       </c>
@@ -4594,8 +4672,14 @@
       <c r="K16" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="30">
+      <c r="L16" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'StaffDirectorySpanishTransfer', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'StaffDirectorySpanishTransfer', 'outcome_type'] ='Staff directory'
+last_act.loc[last_act['Activity Name'] == 'StaffDirectorySpanishTransfer', 'outcome_source'] ='StaffDirectorySpanishTransfer'</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="30">
       <c r="A17" s="15" t="s">
         <v>76</v>
       </c>
@@ -4613,7 +4697,7 @@
         <v>230</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
@@ -4628,8 +4712,14 @@
       <c r="K17" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer', 'outcome_type'] ='Interpreter needed (FD, Legal menu)'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer', 'outcome_source'] ='FrontDeskTransfer'</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="15" t="s">
         <v>50</v>
       </c>
@@ -4639,7 +4729,7 @@
       <c r="C18" s="8">
         <v>2394</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="9">
         <f t="shared" si="0"/>
         <v>9.6360518752867871E-3</v>
       </c>
@@ -4660,8 +4750,14 @@
       <c r="K18" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'TenantMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'TenantMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'TenantMenu', 'outcome_source'] ='TenantMenu'</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="15" t="s">
         <v>79</v>
       </c>
@@ -4679,7 +4775,7 @@
         <v>234</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -4692,8 +4788,14 @@
       <c r="K19" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'CriminalRecordsVoicemailTransfer', 'outcome'] = 'Positive '
+last_act.loc[last_act['Activity Name'] == 'CriminalRecordsVoicemailTransfer', 'outcome_type'] ='Criminal Voicemail'
+last_act.loc[last_act['Activity Name'] == 'CriminalRecordsVoicemailTransfer', 'outcome_source'] ='CriminalRecordsVoicemailTransfer'</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="15" t="s">
         <v>54</v>
       </c>
@@ -4724,8 +4826,14 @@
       <c r="K20" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'OtherLegalOtherMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalOtherMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalOtherMenu', 'outcome_source'] ='OtherLegalOtherMenu'</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="15" t="s">
         <v>53</v>
       </c>
@@ -4756,8 +4864,14 @@
       <c r="K21" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="77.25">
+      <c r="L21" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'DivorceOrParentingMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'DivorceOrParentingMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'DivorceOrParentingMenu', 'outcome_source'] ='DivorceOrParentingMenu'</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="77.25">
       <c r="A22" s="15" t="s">
         <v>63</v>
       </c>
@@ -4788,8 +4902,14 @@
       <c r="K22" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'QueueMenu1', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'QueueMenu1', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'QueueMenu1', 'outcome_source'] ='QueueMenu1'</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="15" t="s">
         <v>35</v>
       </c>
@@ -4820,8 +4940,14 @@
       <c r="K23" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'LegalMenu1', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'LegalMenu1', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'LegalMenu1', 'outcome_source'] ='LegalMenu1'</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="15" t="s">
         <v>34</v>
       </c>
@@ -4831,7 +4957,7 @@
       <c r="C24" s="8">
         <v>1209</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="18">
         <f t="shared" si="0"/>
         <v>4.8663269495495933E-3</v>
       </c>
@@ -4852,8 +4978,14 @@
       <c r="K24" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SeniorsMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SeniorsMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SeniorsMenu', 'outcome_source'] ='SeniorsMenu'</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="15" t="s">
         <v>71</v>
       </c>
@@ -4863,7 +4995,7 @@
       <c r="C25" s="8">
         <v>870</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="18">
         <f t="shared" si="0"/>
         <v>3.5018233631994591E-3</v>
       </c>
@@ -4884,8 +5016,14 @@
       <c r="K25" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'TenantDeterrenceMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'TenantDeterrenceMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'TenantDeterrenceMenu', 'outcome_source'] ='TenantDeterrenceMenu'</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="15" t="s">
         <v>45</v>
       </c>
@@ -4895,7 +5033,7 @@
       <c r="C26" s="8">
         <v>837</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="18">
         <f t="shared" si="0"/>
         <v>3.3689955804574105E-3</v>
       </c>
@@ -4916,8 +5054,14 @@
       <c r="K26" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'HousingMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'HousingMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'HousingMenu', 'outcome_source'] ='HousingMenu'</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="15" t="s">
         <v>100</v>
       </c>
@@ -4927,7 +5071,7 @@
       <c r="C27" s="8">
         <v>836</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="18">
         <f t="shared" si="0"/>
         <v>3.3649704961318939E-3</v>
       </c>
@@ -4935,7 +5079,7 @@
         <v>227</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -4948,8 +5092,14 @@
       <c r="K27" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="77.25">
+      <c r="L27" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'HIVVoicemailTransfer', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'HIVVoicemailTransfer', 'outcome_type'] ='HIV Voicemail'
+last_act.loc[last_act['Activity Name'] == 'HIVVoicemailTransfer', 'outcome_source'] ='HIVVoicemailTransfer'</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="77.25">
       <c r="A28" s="15" t="s">
         <v>60</v>
       </c>
@@ -4959,7 +5109,7 @@
       <c r="C28" s="8">
         <v>785</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="18">
         <f t="shared" si="0"/>
         <v>3.1596911955305462E-3</v>
       </c>
@@ -4980,8 +5130,14 @@
       <c r="K28" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'PlayMOH300s', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'PlayMOH300s', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'PlayMOH300s', 'outcome_source'] ='PlayMOH300s'</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="15" t="s">
         <v>82</v>
       </c>
@@ -4991,7 +5147,7 @@
       <c r="C29" s="8">
         <v>771</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="18">
         <f t="shared" si="0"/>
         <v>3.1033400149733138E-3</v>
       </c>
@@ -5012,8 +5168,14 @@
       <c r="K29" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="195">
+      <c r="L29" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'HIVMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'HIVMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'HIVMenu', 'outcome_source'] ='HIVMenu'</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="195">
       <c r="A30" s="15" t="s">
         <v>102</v>
       </c>
@@ -5023,7 +5185,7 @@
       <c r="C30" s="10">
         <v>694</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="19">
         <f t="shared" si="0"/>
         <v>2.793408521908534E-3</v>
       </c>
@@ -5035,7 +5197,7 @@
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>212</v>
@@ -5044,8 +5206,14 @@
       <c r="K30" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="30">
+      <c r="L30" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ScreenPopProcessComplete', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'ScreenPopProcessComplete', 'outcome_type'] ='Connected to agent'
+last_act.loc[last_act['Activity Name'] == 'ScreenPopProcessComplete', 'outcome_source'] ='ScreenPopProcessComplete'</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="30">
       <c r="A31" s="15" t="s">
         <v>74</v>
       </c>
@@ -5055,7 +5223,7 @@
       <c r="C31" s="8">
         <v>672</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="18">
         <f t="shared" si="0"/>
         <v>2.7048566667471682E-3</v>
       </c>
@@ -5063,7 +5231,7 @@
         <v>234</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
@@ -5078,8 +5246,14 @@
       <c r="K31" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'AddressFaxHoursMenu', 'outcome'] = 'Positive '
+last_act.loc[last_act['Activity Name'] == 'AddressFaxHoursMenu', 'outcome_type'] ='Address Voicemail'
+last_act.loc[last_act['Activity Name'] == 'AddressFaxHoursMenu', 'outcome_source'] ='AddressFaxHoursMenu'</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="15" t="s">
         <v>47</v>
       </c>
@@ -5089,7 +5263,7 @@
       <c r="C32" s="8">
         <v>604</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="18">
         <f t="shared" si="0"/>
         <v>2.4311509326120384E-3</v>
       </c>
@@ -5110,8 +5284,14 @@
       <c r="K32" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'PreTenantMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'PreTenantMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'PreTenantMenu', 'outcome_source'] ='PreTenantMenu'</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="15" t="s">
         <v>42</v>
       </c>
@@ -5121,7 +5301,7 @@
       <c r="C33" s="8">
         <v>543</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="18">
         <f t="shared" si="0"/>
         <v>2.1856207887555245E-3</v>
       </c>
@@ -5142,8 +5322,14 @@
       <c r="K33" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="30">
+      <c r="L33" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'FamilyMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'FamilyMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'FamilyMenu', 'outcome_source'] ='FamilyMenu'</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="30">
       <c r="A34" s="15" t="s">
         <v>110</v>
       </c>
@@ -5153,7 +5339,7 @@
       <c r="C34" s="8">
         <v>541</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="18">
         <f t="shared" si="0"/>
         <v>2.1775706201044914E-3</v>
       </c>
@@ -5161,7 +5347,7 @@
         <v>230</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
@@ -5176,8 +5362,14 @@
       <c r="K34" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer3', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer3', 'outcome_type'] ='No selection on Main menu (FD3)'
+last_act.loc[last_act['Activity Name'] == 'FrontDeskTransfer3', 'outcome_source'] ='FrontDeskTransfer3'</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="15" t="s">
         <v>80</v>
       </c>
@@ -5187,7 +5379,7 @@
       <c r="C35" s="8">
         <v>540</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="18">
         <f t="shared" si="0"/>
         <v>2.1735455357789744E-3</v>
       </c>
@@ -5208,8 +5400,14 @@
       <c r="K35" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ChildSupportMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'ChildSupportMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'ChildSupportMenu', 'outcome_source'] ='ChildSupportMenu'</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="15" t="s">
         <v>73</v>
       </c>
@@ -5219,7 +5417,7 @@
       <c r="C36" s="8">
         <v>527</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="18">
         <f t="shared" si="0"/>
         <v>2.1212194395472585E-3</v>
       </c>
@@ -5240,8 +5438,14 @@
       <c r="K36" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ImmigrationMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'ImmigrationMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'ImmigrationMenu', 'outcome_source'] ='ImmigrationMenu'</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="15" t="s">
         <v>46</v>
       </c>
@@ -5251,7 +5455,7 @@
       <c r="C37" s="8">
         <v>502</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="18">
         <f t="shared" si="0"/>
         <v>2.020592331409343E-3</v>
       </c>
@@ -5272,8 +5476,14 @@
       <c r="K37" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SeniorsADAPTMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SeniorsADAPTMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SeniorsADAPTMenu', 'outcome_source'] ='SeniorsADAPTMenu'</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="15" t="s">
         <v>83</v>
       </c>
@@ -5283,7 +5493,7 @@
       <c r="C38" s="8">
         <v>479</v>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="18">
         <f t="shared" si="0"/>
         <v>1.9280153919224608E-3</v>
       </c>
@@ -5304,8 +5514,14 @@
       <c r="K38" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'OtherLegalPersonalInjuryMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalPersonalInjuryMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalPersonalInjuryMenu', 'outcome_source'] ='OtherLegalPersonalInjuryMenu'</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="15" t="s">
         <v>81</v>
       </c>
@@ -5315,7 +5531,7 @@
       <c r="C39" s="8">
         <v>454</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="18">
         <f t="shared" si="0"/>
         <v>1.8273882837845452E-3</v>
       </c>
@@ -5336,8 +5552,14 @@
       <c r="K39" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'OtherLegalCriminalCaseMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalCriminalCaseMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'OtherLegalCriminalCaseMenu', 'outcome_source'] ='OtherLegalCriminalCaseMenu'</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="15" t="s">
         <v>39</v>
       </c>
@@ -5347,7 +5569,7 @@
       <c r="C40" s="8">
         <v>444</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="18">
         <f t="shared" si="0"/>
         <v>1.7871374405293791E-3</v>
       </c>
@@ -5368,8 +5590,14 @@
       <c r="K40" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SuburbsOrCityMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SuburbsOrCityMenu', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'SuburbsOrCityMenu', 'outcome_source'] ='SuburbsOrCityMenu'</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="15" t="s">
         <v>64</v>
       </c>
@@ -5379,7 +5607,7 @@
       <c r="C41" s="8">
         <v>442</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="18">
         <f t="shared" si="0"/>
         <v>1.779087271878346E-3</v>
       </c>
@@ -5400,40 +5628,52 @@
       <c r="K41" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" ht="60">
+      <c r="L41" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SuburbanSeniorsMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SuburbanSeniorsMenu', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'SuburbanSeniorsMenu', 'outcome_source'] ='SuburbanSeniorsMenu'</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="60">
       <c r="A42" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="5" t="s">
         <v>249</v>
       </c>
       <c r="C42" s="10">
         <v>412</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="19">
         <f t="shared" si="0"/>
         <v>1.6583347421128473E-3</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="F42" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18" t="s">
+      <c r="F42" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="I42" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18">
+      <c r="I42" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'TransferToSafeHaven', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'TransferToSafeHaven', 'outcome_type'] ='Chatbot experiment (Family menu)'
+last_act.loc[last_act['Activity Name'] == 'TransferToSafeHaven', 'outcome_source'] ='TransferToSafeHaven'</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" s="15" t="s">
         <v>77</v>
       </c>
@@ -5443,7 +5683,7 @@
       <c r="C43" s="8">
         <v>353</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="18">
         <f t="shared" si="0"/>
         <v>1.4208547669073666E-3</v>
       </c>
@@ -5464,8 +5704,14 @@
       <c r="K43" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SimpleDivorceMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'SimpleDivorceMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'SimpleDivorceMenu', 'outcome_source'] ='SimpleDivorceMenu'</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" s="15" t="s">
         <v>66</v>
       </c>
@@ -5475,7 +5721,7 @@
       <c r="C44" s="8">
         <v>298</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="18">
         <f t="shared" si="0"/>
         <v>1.1994751290039527E-3</v>
       </c>
@@ -5496,8 +5742,14 @@
       <c r="K44" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" ht="45">
+      <c r="L44" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'BenefitsMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'BenefitsMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'BenefitsMenu', 'outcome_source'] ='BenefitsMenu'</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="45">
       <c r="A45" s="15" t="s">
         <v>69</v>
       </c>
@@ -5507,7 +5759,7 @@
       <c r="C45" s="13">
         <v>278</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="20">
         <f t="shared" si="0"/>
         <v>1.1189734424936202E-3</v>
       </c>
@@ -5530,8 +5782,14 @@
       <c r="K45" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" ht="30">
+      <c r="L45" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SubSeniorPreQueueMessage1_1', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorPreQueueMessage1_1', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorPreQueueMessage1_1', 'outcome_source'] ='SubSeniorPreQueueMessage1_1'</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="30">
       <c r="A46" s="15" t="s">
         <v>105</v>
       </c>
@@ -5541,7 +5799,7 @@
       <c r="C46" s="8">
         <v>228</v>
       </c>
-      <c r="D46" s="20">
+      <c r="D46" s="18">
         <f t="shared" si="0"/>
         <v>9.1771922621778929E-4</v>
       </c>
@@ -5564,8 +5822,14 @@
       <c r="K46" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="77.25">
+      <c r="L46" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ThankYouGoodbye', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'ThankYouGoodbye', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'ThankYouGoodbye', 'outcome_source'] ='ThankYouGoodbye'</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="77.25">
       <c r="A47" s="15" t="s">
         <v>67</v>
       </c>
@@ -5575,7 +5839,7 @@
       <c r="C47" s="8">
         <v>219</v>
       </c>
-      <c r="D47" s="20">
+      <c r="D47" s="18">
         <f t="shared" si="0"/>
         <v>8.8149346728813973E-4</v>
       </c>
@@ -5598,8 +5862,14 @@
       <c r="K47" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'IntakePreQueueMessage1', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'IntakePreQueueMessage1', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'IntakePreQueueMessage1', 'outcome_source'] ='IntakePreQueueMessage1'</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" s="15" t="s">
         <v>38</v>
       </c>
@@ -5609,7 +5879,7 @@
       <c r="C48" s="8">
         <v>212</v>
       </c>
-      <c r="D48" s="20">
+      <c r="D48" s="18">
         <f t="shared" si="0"/>
         <v>8.533178770095233E-4</v>
       </c>
@@ -5630,8 +5900,14 @@
       <c r="K48" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="L48" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SeniorsConfirmationMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SeniorsConfirmationMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SeniorsConfirmationMenu', 'outcome_source'] ='SeniorsConfirmationMenu'</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" s="15" t="s">
         <v>124</v>
       </c>
@@ -5641,7 +5917,7 @@
       <c r="C49" s="8">
         <v>185</v>
       </c>
-      <c r="D49" s="20">
+      <c r="D49" s="18">
         <f t="shared" si="0"/>
         <v>7.446406002205746E-4</v>
       </c>
@@ -5649,7 +5925,7 @@
         <v>227</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -5662,8 +5938,14 @@
       <c r="K49" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="L49" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'VeteransBenefitsVoicemailTransfer', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'VeteransBenefitsVoicemailTransfer', 'outcome_type'] ='Veterans Voicemail'
+last_act.loc[last_act['Activity Name'] == 'VeteransBenefitsVoicemailTransfer', 'outcome_source'] ='VeteransBenefitsVoicemailTransfer'</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="15" t="s">
         <v>70</v>
       </c>
@@ -5673,7 +5955,7 @@
       <c r="C50" s="8">
         <v>183</v>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="18">
         <f t="shared" si="0"/>
         <v>7.3659043156954135E-4</v>
       </c>
@@ -5694,36 +5976,48 @@
       <c r="K50" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" s="19" customFormat="1" ht="30">
+      <c r="L50" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'EmploymentMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'EmploymentMenu', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'EmploymentMenu', 'outcome_source'] ='EmploymentMenu'</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="30">
       <c r="A51" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="B51" s="18"/>
+      <c r="B51" s="5"/>
       <c r="C51" s="10">
         <v>177</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="19">
         <f t="shared" si="0"/>
         <v>7.1243992561644172E-4</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F51" s="18" t="s">
+      <c r="F51" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="I51" s="18" t="s">
+      <c r="G51" s="5"/>
+      <c r="H51" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I51" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-    </row>
-    <row r="52" spans="1:11" ht="30">
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'No activity', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'No activity', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'No activity', 'outcome_source'] ='No activity'</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="30">
       <c r="A52" s="15" t="s">
         <v>128</v>
       </c>
@@ -5733,7 +6027,7 @@
       <c r="C52" s="8">
         <v>158</v>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="18">
         <f t="shared" si="0"/>
         <v>6.3596332343162591E-4</v>
       </c>
@@ -5756,8 +6050,14 @@
       <c r="K52" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="L52" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'DisconnectContact2', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'DisconnectContact2', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'DisconnectContact2', 'outcome_source'] ='DisconnectContact2'</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="15" t="s">
         <v>132</v>
       </c>
@@ -5767,7 +6067,7 @@
       <c r="C53" s="8">
         <v>139</v>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="18">
         <f t="shared" si="0"/>
         <v>5.594867212468101E-4</v>
       </c>
@@ -5775,7 +6075,7 @@
         <v>227</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -5788,8 +6088,14 @@
       <c r="K53" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="L53" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'TraffickingVoicemailTransfer', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'TraffickingVoicemailTransfer', 'outcome_type'] ='Trafficking Voicemail'
+last_act.loc[last_act['Activity Name'] == 'TraffickingVoicemailTransfer', 'outcome_source'] ='TraffickingVoicemailTransfer'</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="15" t="s">
         <v>49</v>
       </c>
@@ -5799,7 +6105,7 @@
       <c r="C54" s="8">
         <v>138</v>
       </c>
-      <c r="D54" s="20">
+      <c r="D54" s="18">
         <f t="shared" si="0"/>
         <v>5.5546163692129352E-4</v>
       </c>
@@ -5820,8 +6126,14 @@
       <c r="K54" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'AppointmentMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'AppointmentMenu', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'AppointmentMenu', 'outcome_source'] ='AppointmentMenu'</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="15" t="s">
         <v>89</v>
       </c>
@@ -5831,7 +6143,7 @@
       <c r="C55" s="8">
         <v>127</v>
       </c>
-      <c r="D55" s="20">
+      <c r="D55" s="18">
         <f t="shared" si="0"/>
         <v>5.1118570934061071E-4</v>
       </c>
@@ -5852,8 +6164,14 @@
       <c r="K55" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SeniorNotCookCoMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'SeniorNotCookCoMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'SeniorNotCookCoMenu', 'outcome_source'] ='SeniorNotCookCoMenu'</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="15" t="s">
         <v>96</v>
       </c>
@@ -5863,7 +6181,7 @@
       <c r="C56" s="8">
         <v>116</v>
       </c>
-      <c r="D56" s="20">
+      <c r="D56" s="18">
         <f t="shared" si="0"/>
         <v>4.669097817599279E-4</v>
       </c>
@@ -5884,8 +6202,14 @@
       <c r="K56" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ImmigrationOtherMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'ImmigrationOtherMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'ImmigrationOtherMenu', 'outcome_source'] ='ImmigrationOtherMenu'</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="15" t="s">
         <v>78</v>
       </c>
@@ -5895,7 +6219,7 @@
       <c r="C57" s="8">
         <v>85</v>
       </c>
-      <c r="D57" s="20">
+      <c r="D57" s="18">
         <f t="shared" si="0"/>
         <v>3.4213216766891265E-4</v>
       </c>
@@ -5903,7 +6227,7 @@
         <v>230</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -5916,8 +6240,14 @@
       <c r="K57" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" ht="90">
+      <c r="L57" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'HolidayPrompt', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'HolidayPrompt', 'outcome_type'] ='Closed hours'
+last_act.loc[last_act['Activity Name'] == 'HolidayPrompt', 'outcome_source'] ='HolidayPrompt'</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="90">
       <c r="A58" s="5" t="s">
         <v>142</v>
       </c>
@@ -5927,7 +6257,7 @@
       <c r="C58" s="8">
         <v>70</v>
       </c>
-      <c r="D58" s="20">
+      <c r="D58" s="18">
         <f t="shared" si="0"/>
         <v>2.8175590278616339E-4</v>
       </c>
@@ -5935,7 +6265,7 @@
         <v>207</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
@@ -5950,8 +6280,14 @@
       <c r="K58" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" ht="30">
+      <c r="L58" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'DisconnectCallbackContact', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'DisconnectCallbackContact', 'outcome_type'] ='Failed courtsey callback'
+last_act.loc[last_act['Activity Name'] == 'DisconnectCallbackContact', 'outcome_source'] ='DisconnectCallbackContact'</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="30">
       <c r="A59" s="15" t="s">
         <v>144</v>
       </c>
@@ -5961,7 +6297,7 @@
       <c r="C59" s="8">
         <v>67</v>
       </c>
-      <c r="D59" s="20">
+      <c r="D59" s="18">
         <f t="shared" si="0"/>
         <v>2.6968064980961351E-4</v>
       </c>
@@ -5969,7 +6305,7 @@
         <v>227</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
@@ -5984,8 +6320,14 @@
       <c r="K59" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" ht="30">
+      <c r="L59" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'MigrantVoicemailTransfer', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'MigrantVoicemailTransfer', 'outcome_type'] ='Farmworker Voicemail'
+last_act.loc[last_act['Activity Name'] == 'MigrantVoicemailTransfer', 'outcome_source'] ='MigrantVoicemailTransfer'</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="30">
       <c r="A60" s="5" t="s">
         <v>92</v>
       </c>
@@ -5995,7 +6337,7 @@
       <c r="C60" s="8">
         <v>58</v>
       </c>
-      <c r="D60" s="20">
+      <c r="D60" s="18">
         <f t="shared" si="0"/>
         <v>2.3345489087996395E-4</v>
       </c>
@@ -6003,7 +6345,7 @@
         <v>227</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
@@ -6018,8 +6360,14 @@
       <c r="K60" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" ht="90">
+      <c r="L60" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ComplimentOrComplaintMenu', 'outcome'] = 'Positive'
+last_act.loc[last_act['Activity Name'] == 'ComplimentOrComplaintMenu', 'outcome_type'] ='Feedback'
+last_act.loc[last_act['Activity Name'] == 'ComplimentOrComplaintMenu', 'outcome_source'] ='ComplimentOrComplaintMenu'</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="90">
       <c r="A61" s="15" t="s">
         <v>52</v>
       </c>
@@ -6029,7 +6377,7 @@
       <c r="C61" s="8">
         <v>37</v>
       </c>
-      <c r="D61" s="20">
+      <c r="D61" s="18">
         <f t="shared" si="0"/>
         <v>1.4892812004411492E-4</v>
       </c>
@@ -6050,8 +6398,14 @@
       <c r="K61" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="L61" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'PreQueueMessage2', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'PreQueueMessage2', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'PreQueueMessage2', 'outcome_source'] ='PreQueueMessage2'</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" s="15" t="s">
         <v>51</v>
       </c>
@@ -6061,7 +6415,7 @@
       <c r="C62" s="8">
         <v>34</v>
       </c>
-      <c r="D62" s="20">
+      <c r="D62" s="18">
         <f t="shared" si="0"/>
         <v>1.3685286706756507E-4</v>
       </c>
@@ -6082,8 +6436,14 @@
       <c r="K62" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" ht="30">
+      <c r="L62" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'HelpWithLegalorOtherReasonMenu', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'HelpWithLegalorOtherReasonMenu', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'HelpWithLegalorOtherReasonMenu', 'outcome_source'] ='HelpWithLegalorOtherReasonMenu'</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="30">
       <c r="A63" s="5" t="s">
         <v>57</v>
       </c>
@@ -6091,7 +6451,7 @@
       <c r="C63" s="8">
         <v>32</v>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="18">
         <f t="shared" si="0"/>
         <v>1.2880269841653182E-4</v>
       </c>
@@ -6099,7 +6459,7 @@
         <v>207</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="s">
@@ -6114,8 +6474,14 @@
       <c r="K63" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="L63" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'DisconnectContact', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'DisconnectContact', 'outcome_type'] ='Outbound call failed'
+last_act.loc[last_act['Activity Name'] == 'DisconnectContact', 'outcome_source'] ='DisconnectContact'</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" s="15" t="s">
         <v>126</v>
       </c>
@@ -6125,7 +6491,7 @@
       <c r="C64" s="8">
         <v>31</v>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="18">
         <f t="shared" si="0"/>
         <v>1.247776140910152E-4</v>
       </c>
@@ -6146,8 +6512,14 @@
       <c r="K64" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" ht="135">
+      <c r="L64" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'WorkersCompMenu', 'outcome'] = 'Neutral'
+last_act.loc[last_act['Activity Name'] == 'WorkersCompMenu', 'outcome_type'] ='LAC does not serve'
+last_act.loc[last_act['Activity Name'] == 'WorkersCompMenu', 'outcome_source'] ='WorkersCompMenu'</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="135">
       <c r="A65" s="5" t="s">
         <v>98</v>
       </c>
@@ -6157,7 +6529,7 @@
       <c r="C65" s="8">
         <v>27</v>
       </c>
-      <c r="D65" s="20">
+      <c r="D65" s="18">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
@@ -6169,7 +6541,7 @@
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>212</v>
@@ -6180,8 +6552,14 @@
       <c r="K65" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" ht="90">
+      <c r="L65" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorTenantAgents', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorTenantAgents', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorTenantAgents', 'outcome_source'] ='GetLoggedInSubSeniorTenantAgents'</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="90">
       <c r="A66" s="5" t="s">
         <v>59</v>
       </c>
@@ -6191,7 +6569,7 @@
       <c r="C66" s="8">
         <v>27</v>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="18">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
@@ -6199,7 +6577,7 @@
         <v>207</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
@@ -6214,8 +6592,14 @@
       <c r="K66" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" ht="45">
+      <c r="L66" t="str">
+        <f t="shared" si="1"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ReadANI', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'ReadANI', 'outcome_type'] ='Failed courtsey callback'
+last_act.loc[last_act['Activity Name'] == 'ReadANI', 'outcome_source'] ='ReadANI'</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="45">
       <c r="A67" s="5" t="s">
         <v>166</v>
       </c>
@@ -6225,8 +6609,8 @@
       <c r="C67" s="8">
         <v>22</v>
       </c>
-      <c r="D67" s="20">
-        <f t="shared" ref="D67:D83" si="1">C67/SUM(($C$2:$C$83))</f>
+      <c r="D67" s="18">
+        <f t="shared" ref="D67:D83" si="2">C67/SUM(($C$2:$C$83))</f>
         <v>8.855185516136563E-5</v>
       </c>
       <c r="E67" s="5" t="s">
@@ -6248,8 +6632,14 @@
       <c r="K67" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" ht="90">
+      <c r="L67" t="str">
+        <f t="shared" ref="L67:L83" si="3">_xlfn.CONCAT("last_act.loc[last_act['Activity Name'] == ","'",A67,"'", ", 'outcome'] = ","'",E67,"'",CHAR(10),"last_act.loc[last_act['Activity Name'] == ","'",A67,"'", ", 'outcome_type'] =","'", F67,"'",CHAR(10),"last_act.loc[last_act['Activity Name'] == ","'",A67,"'", ", 'outcome_source'] =","'", A67,"'")</f>
+        <v>last_act.loc[last_act['Activity Name'] == 'PlayErrorMessage', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'PlayErrorMessage', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'PlayErrorMessage', 'outcome_source'] ='PlayErrorMessage'</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="90">
       <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
@@ -6259,15 +6649,15 @@
       <c r="C68" s="8">
         <v>13</v>
       </c>
-      <c r="D68" s="20">
-        <f t="shared" si="1"/>
+      <c r="D68" s="18">
+        <f t="shared" si="2"/>
         <v>5.2326096231716057E-5</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>207</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -6280,8 +6670,14 @@
       <c r="K68" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="75">
+      <c r="L68" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'CallbackRetry', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'CallbackRetry', 'outcome_type'] ='Failed courtsey callback'
+last_act.loc[last_act['Activity Name'] == 'CallbackRetry', 'outcome_source'] ='CallbackRetry'</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="75">
       <c r="A69" s="5" t="s">
         <v>86</v>
       </c>
@@ -6291,8 +6687,8 @@
       <c r="C69" s="8">
         <v>8</v>
       </c>
-      <c r="D69" s="20">
-        <f t="shared" si="1"/>
+      <c r="D69" s="18">
+        <f t="shared" si="2"/>
         <v>3.2200674604132955E-5</v>
       </c>
       <c r="E69" s="5" t="s">
@@ -6314,8 +6710,14 @@
       <c r="K69" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" ht="90">
+      <c r="L69" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorOtherAgents', 'outcome'] = 'Negative '
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorOtherAgents', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorOtherAgents', 'outcome_source'] ='GetLoggedInSubSeniorOtherAgents'</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="90">
       <c r="A70" s="5" t="s">
         <v>94</v>
       </c>
@@ -6325,8 +6727,8 @@
       <c r="C70" s="8">
         <v>5</v>
       </c>
-      <c r="D70" s="20">
-        <f t="shared" si="1"/>
+      <c r="D70" s="18">
+        <f t="shared" si="2"/>
         <v>2.0125421627583099E-5</v>
       </c>
       <c r="E70" s="5" t="s">
@@ -6348,8 +6750,14 @@
       <c r="K70" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" ht="90">
+      <c r="L70" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'CollectCallbackNumber', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'CollectCallbackNumber', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'CollectCallbackNumber', 'outcome_source'] ='CollectCallbackNumber'</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="90">
       <c r="A71" s="5" t="s">
         <v>95</v>
       </c>
@@ -6359,8 +6767,8 @@
       <c r="C71" s="8">
         <v>4</v>
       </c>
-      <c r="D71" s="20">
-        <f t="shared" si="1"/>
+      <c r="D71" s="18">
+        <f t="shared" si="2"/>
         <v>1.6100337302066478E-5</v>
       </c>
       <c r="E71" s="5" t="s">
@@ -6382,8 +6790,14 @@
       <c r="K71" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="L71" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ConfirmCallbackNumber', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'ConfirmCallbackNumber', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'ConfirmCallbackNumber', 'outcome_source'] ='ConfirmCallbackNumber'</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72" s="12" t="s">
         <v>125</v>
       </c>
@@ -6393,8 +6807,8 @@
       <c r="C72" s="13">
         <v>4</v>
       </c>
-      <c r="D72" s="23">
-        <f t="shared" si="1"/>
+      <c r="D72" s="20">
+        <f t="shared" si="2"/>
         <v>1.6100337302066478E-5</v>
       </c>
       <c r="E72" s="5" t="s">
@@ -6414,8 +6828,14 @@
       <c r="K72" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" ht="75">
+      <c r="L72" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SubSeniorPreQueueMessage1_2', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorPreQueueMessage1_2', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'SubSeniorPreQueueMessage1_2', 'outcome_source'] ='SubSeniorPreQueueMessage1_2'</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="75">
       <c r="A73" s="5" t="s">
         <v>129</v>
       </c>
@@ -6425,8 +6845,8 @@
       <c r="C73" s="8">
         <v>2</v>
       </c>
-      <c r="D73" s="20">
-        <f t="shared" si="1"/>
+      <c r="D73" s="18">
+        <f t="shared" si="2"/>
         <v>8.0501686510332388E-6</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -6448,8 +6868,14 @@
       <c r="K73" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" ht="60">
+      <c r="L73" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorOtherSPAgents', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorOtherSPAgents', 'outcome_type'] ='Abandoned '
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorOtherSPAgents', 'outcome_source'] ='GetLoggedInSubSeniorOtherSPAgents'</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="60">
       <c r="A74" s="5" t="s">
         <v>91</v>
       </c>
@@ -6459,8 +6885,8 @@
       <c r="C74" s="8">
         <v>2</v>
       </c>
-      <c r="D74" s="20">
-        <f t="shared" si="1"/>
+      <c r="D74" s="18">
+        <f t="shared" si="2"/>
         <v>8.0501686510332388E-6</v>
       </c>
       <c r="E74" s="5" t="s">
@@ -6482,8 +6908,14 @@
       <c r="K74" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" ht="75">
+      <c r="L74" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SubSeniorOtherQueue', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorOtherQueue', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorOtherQueue', 'outcome_source'] ='SubSeniorOtherQueue'</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="75">
       <c r="A75" s="5" t="s">
         <v>85</v>
       </c>
@@ -6493,8 +6925,8 @@
       <c r="C75" s="8">
         <v>1</v>
       </c>
-      <c r="D75" s="20">
-        <f t="shared" si="1"/>
+      <c r="D75" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E75" s="5" t="s">
@@ -6516,8 +6948,14 @@
       <c r="K75" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" ht="60">
+      <c r="L75" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'GetLoggedInConsumerAgents', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInConsumerAgents', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInConsumerAgents', 'outcome_source'] ='GetLoggedInConsumerAgents'</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="60">
       <c r="A76" s="5" t="s">
         <v>127</v>
       </c>
@@ -6527,8 +6965,8 @@
       <c r="C76" s="8">
         <v>1</v>
       </c>
-      <c r="D76" s="20">
-        <f t="shared" si="1"/>
+      <c r="D76" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E76" s="5" t="s">
@@ -6550,8 +6988,14 @@
       <c r="K76" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" ht="75">
+      <c r="L76" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'ImmigrationSPQueue', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'ImmigrationSPQueue', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'ImmigrationSPQueue', 'outcome_source'] ='ImmigrationSPQueue'</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="75">
       <c r="A77" s="5" t="s">
         <v>148</v>
       </c>
@@ -6561,8 +7005,8 @@
       <c r="C77" s="8">
         <v>1</v>
       </c>
-      <c r="D77" s="20">
-        <f t="shared" si="1"/>
+      <c r="D77" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E77" s="5" t="s">
@@ -6584,8 +7028,14 @@
       <c r="K77" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" ht="60">
+      <c r="L77" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'GetLoggedInOtherSubSeniorsAgents', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInOtherSubSeniorsAgents', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInOtherSubSeniorsAgents', 'outcome_source'] ='GetLoggedInOtherSubSeniorsAgents'</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="60">
       <c r="A78" s="5" t="s">
         <v>103</v>
       </c>
@@ -6595,8 +7045,8 @@
       <c r="C78" s="8">
         <v>1</v>
       </c>
-      <c r="D78" s="20">
-        <f t="shared" si="1"/>
+      <c r="D78" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E78" s="5" t="s">
@@ -6618,8 +7068,14 @@
       <c r="K78" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" ht="60">
+      <c r="L78" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SubSeniorTenantQueue', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorTenantQueue', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorTenantQueue', 'outcome_source'] ='SubSeniorTenantQueue'</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="60">
       <c r="A79" s="5" t="s">
         <v>176</v>
       </c>
@@ -6629,8 +7085,8 @@
       <c r="C79" s="8">
         <v>1</v>
       </c>
-      <c r="D79" s="20">
-        <f t="shared" si="1"/>
+      <c r="D79" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E79" s="5" t="s">
@@ -6652,8 +7108,14 @@
       <c r="K79" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" ht="150">
+      <c r="L79" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'EducationSPQueue', 'outcome'] = 'Negative '
+last_act.loc[last_act['Activity Name'] == 'EducationSPQueue', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'EducationSPQueue', 'outcome_source'] ='EducationSPQueue'</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="150">
       <c r="A80" s="5" t="s">
         <v>61</v>
       </c>
@@ -6663,19 +7125,19 @@
       <c r="C80" s="8">
         <v>1</v>
       </c>
-      <c r="D80" s="20">
-        <f t="shared" si="1"/>
+      <c r="D80" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>207</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>215</v>
@@ -6686,8 +7148,14 @@
       <c r="K80" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" ht="60">
+      <c r="L80" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'PlayCCBConfirmation', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'PlayCCBConfirmation', 'outcome_type'] ='Failed courtsey callback'
+last_act.loc[last_act['Activity Name'] == 'PlayCCBConfirmation', 'outcome_source'] ='PlayCCBConfirmation'</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="60">
       <c r="A81" s="5" t="s">
         <v>115</v>
       </c>
@@ -6697,8 +7165,8 @@
       <c r="C81" s="8">
         <v>1</v>
       </c>
-      <c r="D81" s="20">
-        <f t="shared" si="1"/>
+      <c r="D81" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -6720,8 +7188,14 @@
       <c r="K81" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" ht="60">
+      <c r="L81" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SubSeniorHomeownerQueue', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorHomeownerQueue', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorHomeownerQueue', 'outcome_source'] ='SubSeniorHomeownerQueue'</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="60">
       <c r="A82" s="5" t="s">
         <v>112</v>
       </c>
@@ -6731,8 +7205,8 @@
       <c r="C82" s="8">
         <v>1</v>
       </c>
-      <c r="D82" s="20">
-        <f t="shared" si="1"/>
+      <c r="D82" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E82" s="5" t="s">
@@ -6754,8 +7228,14 @@
       <c r="K82" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" ht="75">
+      <c r="L82" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'SubSeniorConsumerQueue', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorConsumerQueue', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'SubSeniorConsumerQueue', 'outcome_source'] ='SubSeniorConsumerQueue'</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="75">
       <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
@@ -6765,8 +7245,8 @@
       <c r="C83" s="8">
         <v>1</v>
       </c>
-      <c r="D83" s="20">
-        <f t="shared" si="1"/>
+      <c r="D83" s="18">
+        <f t="shared" si="2"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E83" s="5" t="s">
@@ -6787,6 +7267,12 @@
       </c>
       <c r="K83" s="5">
         <v>2</v>
+      </c>
+      <c r="L83" t="str">
+        <f t="shared" si="3"/>
+        <v>last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorTenantSPAgents', 'outcome'] = 'Negative'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorTenantSPAgents', 'outcome_type'] ='Abandoned'
+last_act.loc[last_act['Activity Name'] == 'GetLoggedInSubSeniorTenantSPAgents', 'outcome_source'] ='GetLoggedInSubSeniorTenantSPAgents'</v>
       </c>
     </row>
   </sheetData>
